--- a/ig/main/ValueSet-jdv-lieu-de-vie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-lieu-de-vie-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260716085852</t>
+    <t>20260911143445</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:58:52+01:00</t>
+    <t>2026-09-11T14:34:45+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-lieu-de-vie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-lieu-de-vie-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260911143445</t>
+    <t>20260916095455</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:34:45+01:00</t>
+    <t>2026-09-16T09:54:55+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-lieu-de-vie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-lieu-de-vie-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260916095455</t>
+    <t>20260928134052</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:54:55+01:00</t>
+    <t>2026-09-28T13:40:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
